--- a/docs/公众号内容盘点表.xlsx
+++ b/docs/公众号内容盘点表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公众号内容盘点" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="公众号内容盘点" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,11 +26,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF175CEB"/>
+      <sz val="10"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -39,12 +59,15 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001e293b"/>
-        <bgColor rgb="001e293b"/>
+        <fgColor rgb="FFE7E6E6"/>
+        <bgColor rgb="FFE7E6E6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill/>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -53,36 +76,87 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="00d1d5db"/>
-      </left>
-      <right style="thin">
-        <color rgb="00d1d5db"/>
-      </right>
-      <top style="thin">
-        <color rgb="00d1d5db"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00d1d5db"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -443,240 +517,804 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="32" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="6" customWidth="1" style="3" min="1" max="1"/>
+    <col width="42" customWidth="1" style="3" min="2" max="2"/>
+    <col width="26" customWidth="1" style="3" min="3" max="3"/>
+    <col width="38" customWidth="1" style="3" min="4" max="4"/>
+    <col width="14" customWidth="1" style="3" min="5" max="5"/>
+    <col width="46" customWidth="1" style="3" min="6" max="6"/>
+    <col width="14" customWidth="1" style="3" min="7" max="7"/>
+    <col width="42" customWidth="1" style="3" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>公众号合集名</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>对应网站 series slug</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>文章标题</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>发布日期</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>原文链接</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>是否需要搬运</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="17" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>大宋纪丽</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>大宋纪历生活之旅 | 第一卷·东京风华·立国卷</t>
+        </is>
+      </c>
+      <c r="C2" s="19" t="inlineStr">
         <is>
           <t>dasongjili</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>点茶不是泡茶：从一盏建盏看宋人的慢</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>https://mp.weixin.qq.com/...</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>已搬运</t>
+      <c r="D2" s="19" t="inlineStr"/>
+      <c r="E2" s="19" t="inlineStr"/>
+      <c r="F2" s="19" t="inlineStr"/>
+      <c r="G2" s="19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H2" s="20" t="inlineStr">
+        <is>
+          <t>已搬运示例合集，后台显示 86 篇，最后更新 09/05 17:31</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>十二生肖职场人格解码</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>十二生肖职场人格解码——生肖职场人格修炼手册</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
         <is>
           <t>shiershengxiao</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>像狗一样守护</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>https://mp.weixin.qq.com/...</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>已搬运</t>
+      <c r="D3" s="19" t="inlineStr"/>
+      <c r="E3" s="19" t="inlineStr"/>
+      <c r="F3" s="19" t="inlineStr"/>
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>已搬运示例合集，后台显示 83 篇，最后更新 09/06 10:11</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="18" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>二十四节气</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>纪历二十四节气生活馆</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>ershisijieqi</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="D4" s="19" t="inlineStr"/>
+      <c r="E4" s="19" t="inlineStr"/>
+      <c r="F4" s="19" t="inlineStr"/>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>后台显示 15 篇，最后更新 09/07 10:08</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>一宋一词</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>《一宋一词》贴图文集（一）</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>yisongyici</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr"/>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
+      <c r="D5" s="19" t="inlineStr"/>
+      <c r="E5" s="19" t="inlineStr"/>
+      <c r="F5" s="19" t="inlineStr"/>
+      <c r="G5" s="19" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="H5" s="20" t="inlineStr">
+        <is>
+          <t>第二页截图显示为「贴图」类型，提示暂不支持合集配置；如以文章形式发布需另整理</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="18" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>纪丽生活馆</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>jilishenghuoguan</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>岁华纪历 | 传统佳节记</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>jiajieji</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr"/>
+      <c r="E6" s="19" t="inlineStr"/>
+      <c r="F6" s="19" t="inlineStr"/>
+      <c r="G6" s="19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>后台显示 6 篇，最后更新 08/19 07:59</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>元一·钻石监理成长圈</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>岁华纪历 | 传统佳节记</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>jiajieji</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>岁华纪历·佳节纪 | 除夕：今夜，折叠时光，存爱入福</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>2026-2-16</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr"/>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>岁华纪历 | 传统佳节记</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>jiajieji</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>岁华纪历·佳节纪 | 春节：今日，我与天地同新</t>
+        </is>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>2026-2-17</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr"/>
+      <c r="G8" s="19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>岁华纪历 | 传统佳节记</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>jiajieji</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>岁华纪历·佳节纪 | 元宵节：灯火可亲，人间皆安</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>2026-3-3</t>
+        </is>
+      </c>
+      <c r="F9" s="19" t="inlineStr"/>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>岁华纪历 | 传统佳节记</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>jiajieji</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>岁华纪历·佳节纪 | 二月二 龙抬头</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>2026-3-20</t>
+        </is>
+      </c>
+      <c r="F10" s="19" t="inlineStr"/>
+      <c r="G10" s="19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>岁华纪历 | 传统佳节记</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>jiajieji</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>岁华纪历·佳节纪 | 端午：端午临中夏，春禧正当时</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr"/>
+      <c r="F11" s="19" t="inlineStr"/>
+      <c r="G11" s="19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>岁华纪历 | 传统佳节记</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>jiajieji</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>岁华纪历·佳节纪 | 七夕：鹊桥相会，人间乞巧</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr"/>
+      <c r="F12" s="19" t="inlineStr"/>
+      <c r="G12" s="19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>监理行业AI落地系列</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>yuanyizuanshi</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr"/>
+      <c r="E13" s="19" t="inlineStr"/>
+      <c r="F13" s="19" t="inlineStr"/>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>后台显示 17 篇，最后更新 08/31 16:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>视频号</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>shipinhao</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
+      <c r="D14" s="19" t="inlineStr"/>
+      <c r="E14" s="19" t="inlineStr"/>
+      <c r="F14" s="19" t="inlineStr"/>
+      <c r="G14" s="19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>视频号内容不属于公众号文章合集，需单独评估迁移方式</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>非遗文化物语</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>feiyi</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr"/>
+      <c r="E15" s="21" t="inlineStr"/>
+      <c r="F15" s="21" t="inlineStr"/>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>待定</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>后台显示 3 篇，类型为「图文」，提示「暂不支持」合集配置；需确认能否以文章形式迁移</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>《你是你吃出来的》笔记系列</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>nishinichichulai</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr"/>
+      <c r="E16" s="21" t="inlineStr"/>
+      <c r="F16" s="21" t="inlineStr"/>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>后台显示 6 篇，最后更新 08/10 16:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>戒瘾的本质</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>jieyindebenzhi</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr"/>
+      <c r="E17" s="21" t="inlineStr"/>
+      <c r="F17" s="21" t="inlineStr"/>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>后台显示 4 篇，最后更新 08/10 16:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>冯仑“三不慕”幸福课</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>fenglun</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr"/>
+      <c r="E18" s="21" t="inlineStr"/>
+      <c r="F18" s="21" t="inlineStr"/>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>后台显示 4 篇，最后更新 08/10 16:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>从心连接：重新定义亲子沟通</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>congxinlianjie</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr"/>
+      <c r="E19" s="21" t="inlineStr"/>
+      <c r="F19" s="21" t="inlineStr"/>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>后台显示 7 篇，最后更新 08/10 16:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>纪历生活体验馆 | 衣、食、住、行四雅系列</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>jilishenghuotiyanguan-siya</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr"/>
+      <c r="E20" s="21" t="inlineStr"/>
+      <c r="F20" s="21" t="inlineStr"/>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>后台显示 5 篇，最后更新 08/10 16:40；slug 待定，需与「纪历生活体验馆」区分</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>钻石监理系列</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>zuanshijianli</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr"/>
+      <c r="E21" s="21" t="inlineStr"/>
+      <c r="F21" s="21" t="inlineStr"/>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>后台显示 12 篇，最后更新 08/10 16:38，访问人数 18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>《AI时代父母养育指南》</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>aifumuyangyu</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr"/>
+      <c r="E22" s="21" t="inlineStr"/>
+      <c r="F22" s="21" t="inlineStr"/>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>后台显示 5 篇，最后更新 08/10 16:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>生肖文化密码系列</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>shengxiaowenhuamima</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr"/>
+      <c r="E23" s="21" t="inlineStr"/>
+      <c r="F23" s="21" t="inlineStr"/>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>后台显示 4 篇，最后更新 08/10 16:32；与十二生肖系列可能相关，需确认是否合并</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>纪历生活体验馆</t>
+        </is>
+      </c>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>jilishenghuotiyanguan</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr"/>
+      <c r="E24" s="21" t="inlineStr"/>
+      <c r="F24" s="21" t="inlineStr"/>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>后台显示 7 篇，最后更新 08/10 16:26；与「衣、食、住、行四雅系列」是不同合集</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>认识复利10讲</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>renshifuli</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr"/>
+      <c r="E25" s="21" t="inlineStr"/>
+      <c r="F25" s="21" t="inlineStr"/>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>后台显示 11 篇，最后更新 08/10 16:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="21" t="inlineStr">
+        <is>
+          <t>何以@岁华纪丽</t>
+        </is>
+      </c>
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>heyi-suihuajili</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr"/>
+      <c r="E26" s="21" t="inlineStr"/>
+      <c r="F26" s="21" t="inlineStr"/>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>后台显示 7 篇，最后更新 08/10 16:23；slug 待定</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>视频 - 认知复利10讲</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>shipin-fuli</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr"/>
+      <c r="E27" s="21" t="inlineStr"/>
+      <c r="F27" s="21" t="inlineStr"/>
+      <c r="G27" s="21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
+        <is>
+          <t>视频合集，提示「暂不支持」；不直接搬运为文章</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
